--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20232.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20232.xlsx
@@ -969,25 +969,25 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1004,25 +1004,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1036,25 +1036,25 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1071,25 +1071,25 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1103,25 +1103,25 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1138,25 +1138,25 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1170,25 +1170,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1205,25 +1205,25 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1237,25 +1237,25 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1272,25 +1272,25 @@
         <v>12</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1304,25 +1304,25 @@
         <v>12</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1333,25 +1333,25 @@
         <v>112</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F13">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1431,7 @@
         <v>16.7</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1454,19 +1454,19 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1486,19 +1486,19 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>95.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1521,19 +1521,19 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H5" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1553,19 +1553,19 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H6" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>7.1</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1734,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>25</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1783,19 +1783,19 @@
         <v>112</v>
       </c>
       <c r="E13">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>91.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="H13" s="1">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20232.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20232.xlsx
@@ -618,22 +618,22 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H5" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -650,22 +650,22 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H6" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -752,22 +752,22 @@
         <v>26</v>
       </c>
       <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
         <v>14</v>
-      </c>
-      <c r="E9">
-        <v>13</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H9" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>18</v>
       </c>
       <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
         <v>14</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H10" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -880,22 +880,22 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F13">
         <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>91.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H13" s="1">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1068,22 +1068,22 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="H5" s="1">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1100,22 +1100,22 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="H6" s="1">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1202,22 +1202,22 @@
         <v>26</v>
       </c>
       <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
         <v>14</v>
-      </c>
-      <c r="E9">
-        <v>13</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H9" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1234,22 +1234,22 @@
         <v>18</v>
       </c>
       <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
         <v>14</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H10" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1330,19 +1330,19 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F13">
         <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>92</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I13" s="2">
         <v>8.4</v>
@@ -1419,19 +1419,19 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>3.3</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1486,19 +1486,19 @@
         <v>42</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>92.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H4" s="1">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="I4" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1518,22 +1518,22 @@
         <v>26</v>
       </c>
       <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
         <v>14</v>
       </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>85.7</v>
+        <v>93.3</v>
       </c>
       <c r="H5" s="1">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1550,22 +1550,22 @@
         <v>18</v>
       </c>
       <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>93.3</v>
       </c>
       <c r="H6" s="1">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1652,22 +1652,22 @@
         <v>26</v>
       </c>
       <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
         <v>14</v>
-      </c>
-      <c r="E9">
-        <v>13</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H9" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1684,22 +1684,22 @@
         <v>18</v>
       </c>
       <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
         <v>14</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H10" s="1">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1734,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>25</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1780,22 +1780,22 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F13">
         <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>92</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I13" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
         <v>0</v>
